--- a/output/2026-09-20_15_Croazia_Splitsko-dalmatinska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-20_15_Croazia_Splitsko-dalmatinska_ATEX_Equipment-Services.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pagina dedicata 'ATEX OPREMA' confermata con menzione di ispettori/tecnici certificati CompEx.</t>
+          <t>Pagina dedicata 'ATEX OPREMA' confermata con menzione di ispettori/tecnici certificati CompEx. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">

--- a/output/2026-09-20_15_Croazia_Splitsko-dalmatinska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-20_15_Croazia_Splitsko-dalmatinska_ATEX_Equipment-Services.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-20_15_Croazia_Splitsko-dalmatinska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-20_15_Croazia_Splitsko-dalmatinska_ATEX_Equipment-Services.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Azienda leader nel settore protezione antiesplosione in Croazia. Copertura Split plausibile non esplicita.</t>
+          <t>Azienda leader nel settore protezione antiesplosione in Croazia. Copertura Split plausibile non esplicita. [DUPLICATO — vedi anche: 2026-09-13_16_Croazia_Bjelovarsko-bilogorska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pagina dedicata 'Protueksplozijska zaštita (Ex)' confermata; ente storico dal 1998.</t>
+          <t>Pagina dedicata 'Protueksplozijska zaštita (Ex)' confermata; ente storico dal 1998. [DUPLICATO — vedi anche: 2026-09-15_15_Croazia_Pozesko-slavonska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Confermato come ente autorizzato in Croazia per test di atmosfere esplosive. Attivo dal 1992.</t>
+          <t>Confermato come ente autorizzato in Croazia per test di atmosfere esplosive. Attivo dal 1992. [DUPLICATO — vedi anche: 2026-09-16_17_Croazia_Zadarska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Prodotto dedicato 'EB EX-ATEX' confermato; ventilatori assiali in versione Ex-ATEX su richiesta, servizio su tutta la Croazia.</t>
+          <t>Prodotto dedicato 'EB EX-ATEX' confermato; ventilatori assiali in versione Ex-ATEX su richiesta, servizio su tutta la Croazia. [DUPLICATO — vedi anche: 2026-09-13_08_Croazia_Koprivnicko-krizevacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">

--- a/output/2026-09-20_15_Croazia_Splitsko-dalmatinska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-20_15_Croazia_Splitsko-dalmatinska_ATEX_Equipment-Services.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Confermata linea prodotto dedicata 'Dizalice za Ex zone (ATEX)' sul sito ufficiale; filiale Split confermata da fonte indipendente. Telefono solo sede centrale Zagabria; nessuna email generica reperita.</t>
+          <t>Confermata linea prodotto dedicata 'Dizalice za Ex zone (ATEX)' sul sito ufficiale; filiale Split confermata da fonte indipendente. Telefono solo sede centrale Zagabria; nessuna email generica reperita. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pagina dedicata 'Ispitivanja u Ex-prostoru' confermata; presenza operativa/posizioni aperte anche a Split.</t>
+          <t>Pagina dedicata 'Ispitivanja u Ex-prostoru' confermata; presenza operativa/posizioni aperte anche a Split. [DUPLICATO — vedi anche: 2026-09-13_16_Croazia_Bjelovarsko-bilogorska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
